--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2170,6 +2170,356 @@
       <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136931584</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136950550</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storåbränna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>495712</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7083964</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950550</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136950551</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storåbränna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>495830</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7083591</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Något glesare på västra vägsidan</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950551</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136950357</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98282</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storåbränna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>495674</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7084063</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950357</t>
         </is>
       </c>
     </row>
@@ -2188,6 +2538,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98320</v>
+        <v>98323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98323</v>
+        <v>98333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98333</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98341</v>
+        <v>98347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98363</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8369-2023 artfynd.xlsx
+++ b/artfynd/A 8369-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931235</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136931244</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136931583</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136931237</v>
       </c>
       <c r="B5" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136931238</v>
       </c>
       <c r="B6" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136931240</v>
       </c>
       <c r="B7" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136931242</v>
       </c>
       <c r="B8" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>136931585</v>
       </c>
       <c r="B9" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>136931236</v>
       </c>
       <c r="B10" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136931239</v>
       </c>
       <c r="B11" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136931582</v>
       </c>
       <c r="B12" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136931234</v>
       </c>
       <c r="B13" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>136931584</v>
       </c>
       <c r="B14" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>136950550</v>
       </c>
       <c r="B15" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136950551</v>
       </c>
       <c r="B16" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>136950357</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
